--- a/rsvp_forms/037_form_generator_rsvp_form--rsvp_forms.xlsx
+++ b/rsvp_forms/037_form_generator_rsvp_form--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rsvp_form</t>
+          <t>rsvp_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RSVP Form</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,24 +538,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rsvp_fields</t>
+          <t>rsvp_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RSVP Fields</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Please select your RSVP</t>
-        </is>
-      </c>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -565,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rsvp_time</t>
+          <t>rsvp_phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RSVP Time</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please enter a time</t>
-        </is>
-      </c>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -592,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rsvp_message</t>
+          <t>rsvp_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RSVP Message</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -615,24 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rsvp_email</t>
+          <t>rsvp_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RSVP Email</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter your email address</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -647,19 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rsvp_phone</t>
+          <t>rsvp_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RSVP Phone</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter your phone number</t>
-        </is>
-      </c>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -669,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rsvp_date</t>
+          <t>rsvp_guests</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RSVP Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter a date</t>
-        </is>
-      </c>
+          <t>Are you arriving with any guests?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -696,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rsvp_time</t>
+          <t>rsvp_guests_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RSVP Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter a time</t>
-        </is>
-      </c>
+          <t>What is the number of guests?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -728,19 +704,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rsvp_comments</t>
+          <t>rsvp_requirements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RSVP Comments</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter your comments</t>
-        </is>
-      </c>
+          <t>Do you have any special requirements or requests?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rsvp_fields_1</t>
+          <t>rsvp_attendance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RSVP Fields 1</t>
+          <t>Are you able to attend the event?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -773,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rsvp_fields_2</t>
+          <t>rsvp_additional_events</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RSVP Fields 2</t>
+          <t>Would you like to sign up for any additional activities or events?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rsvp_fields_3</t>
+          <t>rsvp_restrictions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RSVP Fields 3</t>
+          <t>Do you have any dietary restrictions or preferences?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rsvp_fields_4</t>
+          <t>rsvp_comments2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RSVP Fields 4</t>
+          <t>Enter any comments or requests</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rsvp_fields_5</t>
+          <t>rsvp_email2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RSVP Fields 5</t>
+          <t>Enter your email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -865,24 +837,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rsvp_date</t>
+          <t>rsvp_phone2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RSVP Date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter a date</t>
-        </is>
-      </c>
+          <t>Enter your phone</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -892,24 +860,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rsvp_time</t>
+          <t>rsvp_name2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RSVP Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter a time</t>
-        </is>
-      </c>
+          <t>Enter your name</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -919,24 +883,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rsvp_comments</t>
+          <t>rsvp_fields_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RSVP Comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter your comments</t>
-        </is>
-      </c>
+          <t>Select Field 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -946,24 +906,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rsvp_email</t>
+          <t>rsvp_fields_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RSVP Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter your email</t>
-        </is>
-      </c>
+          <t>Select Field 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -973,24 +929,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rsvp_phone</t>
+          <t>rsvp_fields_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RSVP Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter your phone</t>
-        </is>
-      </c>
+          <t>Select Field 3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -1000,156 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rsvp_date</t>
+          <t>rsvp_fields_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RSVP Date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter a date</t>
-        </is>
-      </c>
+          <t>Select Field 4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>RSVP Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Enter a time</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>rsvp_comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>RSVP Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter your comments</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rsvp_email</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>RSVP Email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Enter your email</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rsvp_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>RSVP Phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter your phone</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>rsvp_fields_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>RSVP Fields 6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1166,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,510 +1011,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rsvp_fields_choices</t>
+          <t>rsvp_guests_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rsvp_fields_choices</t>
+          <t>rsvp_guests_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_attendance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_attendance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_additional_events_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_additional_events_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_restrictions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_restrictions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_fields_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>field_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>Field 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_fields_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>field_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>Field 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_fields_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>field_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>Field 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rsvp_time_choices</t>
+          <t>rsvp_fields_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>field_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>Field 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rsvp_fields_1_choices</t>
+          <t>rsvp_fields_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'field1'}</t>
+          <t>field_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'field1'}</t>
+          <t>Field 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rsvp_fields_1_choices</t>
+          <t>rsvp_fields_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'field2'}</t>
+          <t>field_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'field2'}</t>
+          <t>Field 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rsvp_fields_1_choices</t>
+          <t>rsvp_fields_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'field3'}</t>
+          <t>field_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'field3'}</t>
+          <t>Field 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rsvp_fields_2_choices</t>
+          <t>rsvp_fields_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'field1'}</t>
+          <t>field_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'field1'}</t>
+          <t>Field 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rsvp_fields_2_choices</t>
+          <t>rsvp_fields_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'field2'}</t>
+          <t>field_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'field2'}</t>
+          <t>Field 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rsvp_fields_2_choices</t>
+          <t>rsvp_fields_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'field3'}</t>
+          <t>field_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'field3'}</t>
+          <t>Field 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rsvp_fields_3_choices</t>
+          <t>rsvp_fields_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'field1'}</t>
+          <t>field_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'field1'}</t>
+          <t>Field 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rsvp_fields_3_choices</t>
+          <t>rsvp_fields_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'field2'}</t>
+          <t>field_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'field2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>rsvp_fields_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'label':_'field3'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'label': 'field3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>rsvp_fields_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'label':_'field1'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'label': 'field1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>rsvp_fields_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_'field2'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': 'field2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>rsvp_fields_4_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_'field3'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': 'field3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>rsvp_fields_5_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'label':_'field1'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'label': 'field1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>rsvp_fields_5_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_'field2'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': 'field2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>rsvp_fields_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'field3'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'field3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>rsvp_fields_6_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'field1'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'field1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>rsvp_fields_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'label':_'field2'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'label': 'field2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rsvp_fields_6_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'field3'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'field3'}</t>
+          <t>Field 3</t>
         </is>
       </c>
     </row>
